--- a/test_data/norfolk_coastal_flooding/full_benchmarking_experiment_uva_test_gpu_all.xlsx
+++ b/test_data/norfolk_coastal_flooding/full_benchmarking_experiment_uva_test_gpu_all.xlsx
@@ -664,7 +664,7 @@
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>sa_id</t>
+          <t>member_id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
